--- a/sample-data/LD_programs_2026-05.xlsx
+++ b/sample-data/LD_programs_2026-05.xlsx
@@ -439,16 +439,16 @@
         <v>Compliance</v>
       </c>
       <c r="D2" t="str">
-        <v>Self-paced</v>
+        <v>Classroom</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-04-13</v>
+        <v>2026-05-07</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-23</v>
       </c>
       <c r="G2" t="str">
-        <v>Coursera</v>
+        <v>LinkedIn Learning</v>
       </c>
       <c r="H2">
         <v>120000</v>
@@ -468,16 +468,16 @@
         <v>Mandatory</v>
       </c>
       <c r="D3" t="str">
-        <v>Classroom</v>
+        <v>Virtual</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-04-14</v>
+        <v>2026-05-20</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-05-07</v>
+        <v>2026-05-24</v>
       </c>
       <c r="G3" t="str">
-        <v>Coursera</v>
+        <v>UpGrad</v>
       </c>
       <c r="H3">
         <v>90000</v>
@@ -497,16 +497,16 @@
         <v>Compliance</v>
       </c>
       <c r="D4" t="str">
-        <v>Self-paced</v>
+        <v>Virtual</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-05-14</v>
+        <v>2026-04-13</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-06-23</v>
+        <v>2026-05-01</v>
       </c>
       <c r="G4" t="str">
-        <v>LinkedIn Learning</v>
+        <v>Coursera</v>
       </c>
       <c r="H4">
         <v>110000</v>
@@ -529,13 +529,13 @@
         <v>Classroom</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-03-13</v>
+        <v>2026-05-05</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-01</v>
       </c>
       <c r="G5" t="str">
-        <v>UpGrad</v>
+        <v>Coursera</v>
       </c>
       <c r="H5">
         <v>260000</v>
@@ -555,16 +555,16 @@
         <v>Functional</v>
       </c>
       <c r="D6" t="str">
-        <v>Self-paced</v>
+        <v>Classroom</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-04-15</v>
+        <v>2026-05-09</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-06-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="G6" t="str">
-        <v>Coursera</v>
+        <v>UpGrad</v>
       </c>
       <c r="H6">
         <v>180000</v>
@@ -584,16 +584,16 @@
         <v>Functional</v>
       </c>
       <c r="D7" t="str">
-        <v>Self-paced</v>
+        <v>Classroom</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-03</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-06-12</v>
+        <v>2026-05-06</v>
       </c>
       <c r="G7" t="str">
-        <v>Coursera</v>
+        <v>LinkedIn Learning</v>
       </c>
       <c r="H7">
         <v>150000</v>
@@ -613,16 +613,16 @@
         <v>Onboarding</v>
       </c>
       <c r="D8" t="str">
-        <v>Virtual</v>
+        <v>Classroom</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-04-07</v>
+        <v>2026-03-15</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-27</v>
       </c>
       <c r="G8" t="str">
-        <v>Internal L&amp;D</v>
+        <v>UpGrad</v>
       </c>
       <c r="H8">
         <v>80000</v>
@@ -642,16 +642,16 @@
         <v>Compliance</v>
       </c>
       <c r="D9" t="str">
-        <v>Self-paced</v>
+        <v>Classroom</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-08</v>
       </c>
       <c r="G9" t="str">
-        <v>Internal L&amp;D</v>
+        <v>UpGrad</v>
       </c>
       <c r="H9">
         <v>100000</v>
@@ -671,16 +671,16 @@
         <v>Functional</v>
       </c>
       <c r="D10" t="str">
-        <v>Self-paced</v>
+        <v>Classroom</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-04-09</v>
+        <v>2026-05-04</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-24</v>
       </c>
       <c r="G10" t="str">
-        <v>Internal L&amp;D</v>
+        <v>LinkedIn Learning</v>
       </c>
       <c r="H10">
         <v>60000</v>
@@ -700,16 +700,16 @@
         <v>Leadership</v>
       </c>
       <c r="D11" t="str">
-        <v>Self-paced</v>
+        <v>Virtual</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-03-02</v>
+        <v>2026-04-16</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-05-22</v>
+        <v>2026-06-24</v>
       </c>
       <c r="G11" t="str">
-        <v>UpGrad</v>
+        <v>LinkedIn Learning</v>
       </c>
       <c r="H11">
         <v>320000</v>
